--- a/english_business.xlsx
+++ b/english_business.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_scripts\git_repo\english_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B80A14-56CA-4A24-A175-25EBF2A9F404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EA5416-93DC-4501-86DF-6D952C8AB571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8B4C7582-CBEF-480A-B961-73E7B5B85050}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8B4C7582-CBEF-480A-B961-73E7B5B85050}"/>
   </bookViews>
   <sheets>
     <sheet name="Verbs" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Phrases" sheetId="6" r:id="rId5"/>
     <sheet name="Times" sheetId="9" r:id="rId6"/>
     <sheet name="Misc" sheetId="7" r:id="rId7"/>
+    <sheet name="Conditions" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Verbs!$B$1:$B$2</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="206">
   <si>
     <t>What are you working on today?</t>
   </si>
@@ -663,6 +664,30 @@
   </si>
   <si>
     <t xml:space="preserve">in order to </t>
+  </si>
+  <si>
+    <t>"Why don't you" + base verb for friendly suggestions</t>
+  </si>
+  <si>
+    <t>"How about" can suggest trying something simple first</t>
+  </si>
+  <si>
+    <t>already</t>
+  </si>
+  <si>
+    <t>ever</t>
+  </si>
+  <si>
+    <t>yet</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>if , verb in future</t>
+  </si>
+  <si>
+    <t>if , verb in present</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1214,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B14">
@@ -1197,7 +1222,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B15">
@@ -1205,7 +1230,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B16">
@@ -1213,7 +1238,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B17">
@@ -1221,27 +1246,27 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1674,35 +1699,35 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -2546,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D970717-8E87-4676-B39F-876C05598EDE}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.5546875" customWidth="1"/>
@@ -2629,6 +2654,22 @@
         <v>73</v>
       </c>
       <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
     </row>
@@ -2740,7 +2781,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BE1683-B44E-4AAF-88DE-B0E3A73B7CFB}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.21875" customWidth="1"/>
@@ -2839,7 +2880,77 @@
         <v>55</v>
       </c>
       <c r="B12" s="8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4FE87CA-EFD7-4218-BDFB-E0C8C6EEEE7D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
